--- a/SoRoSim Robots/my_robot(1.5)(3tendon)/10-09-2025/Validation(1.5)(3tendon).xlsx
+++ b/SoRoSim Robots/my_robot(1.5)(3tendon)/10-09-2025/Validation(1.5)(3tendon).xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/SoRoSim Robots/my_robot(1.5)(3tendon)/10-09-2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2017" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47DEF5EE-D7F1-4DE1-AC00-5C5E6223F6D8}"/>
+  <xr:revisionPtr revIDLastSave="2033" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65E06915-D108-4373-A059-97679DA20D59}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (single)" sheetId="8" r:id="rId1"/>
     <sheet name="Distal Validation (single)" sheetId="9" r:id="rId2"/>
-    <sheet name="Distal Vali (single, w noise)" sheetId="11" r:id="rId3"/>
-    <sheet name="Conversion" sheetId="4" r:id="rId4"/>
+    <sheet name="Distal Vali (0.2 prop noise)" sheetId="11" r:id="rId3"/>
+    <sheet name="Distal Vali (add noise)" sheetId="13" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId5"/>
+    <sheet name="Conversion" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="33">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -389,6 +391,13 @@
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -401,12 +410,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -416,19 +419,19 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -440,7 +443,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -462,10 +464,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -786,47 +784,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22B4A24-01F9-43FA-AE7F-5A1710EEAA53}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:25" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="11" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="13" t="s">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="17" t="s">
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="19"/>
-    </row>
-    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="20"/>
+    </row>
+    <row r="2" spans="1:25" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,26 +901,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="11">
         <v>0.3</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="11">
         <v>0.08</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="11">
         <v>1.571</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="11">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="11">
         <v>1.4</v>
       </c>
-      <c r="F3" s="28">
-        <v>0</v>
-      </c>
-      <c r="G3" s="28">
+      <c r="F3" s="11">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
         <v>0</v>
       </c>
       <c r="H3" s="9">
@@ -986,26 +984,26 @@
         <v>3.0356762917084973E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="11">
         <v>0.4</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="11">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="11">
         <v>1.571</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="11">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E4" s="28">
-        <v>0</v>
-      </c>
-      <c r="F4" s="28">
-        <v>0</v>
-      </c>
-      <c r="G4" s="28">
+      <c r="E4" s="11">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11">
         <v>0</v>
       </c>
       <c r="H4" s="9">
@@ -1069,26 +1067,26 @@
         <v>4.3861778587547806E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="11">
         <v>0.6</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="11">
         <v>0.16</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="11">
         <v>1.571</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="11">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="11">
         <v>1.4</v>
       </c>
-      <c r="F5" s="28">
-        <v>0</v>
-      </c>
-      <c r="G5" s="28">
+      <c r="F5" s="11">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11">
         <v>0</v>
       </c>
       <c r="H5" s="9">
@@ -1152,26 +1150,26 @@
         <v>4.1193938998757673E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" s="11">
         <v>0.4</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="11">
         <v>0.06</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="11">
         <v>1.571</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="11">
         <v>1.571</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="11">
         <v>1.4</v>
       </c>
-      <c r="F6" s="28">
-        <v>0</v>
-      </c>
-      <c r="G6" s="28">
+      <c r="F6" s="11">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11">
         <v>0</v>
       </c>
       <c r="H6" s="9">
@@ -1235,26 +1233,26 @@
         <v>4.4884785550945883E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7" s="11">
         <v>0.8</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="11">
         <v>0.08</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="11">
         <v>1.571</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="11">
         <v>1.571</v>
       </c>
-      <c r="E7" s="28">
-        <v>0</v>
-      </c>
-      <c r="F7" s="28">
-        <v>0</v>
-      </c>
-      <c r="G7" s="28">
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
         <v>0</v>
       </c>
       <c r="H7" s="9">
@@ -1318,26 +1316,26 @@
         <v>0.10840252226451574</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8" s="11">
         <v>0.7</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="11">
         <v>0.16</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="11">
         <v>1.571</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="11">
         <v>1.571</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="11">
         <v>1.4</v>
       </c>
-      <c r="F8" s="28">
-        <v>0</v>
-      </c>
-      <c r="G8" s="28">
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
         <v>0</v>
       </c>
       <c r="H8" s="9">
@@ -1401,26 +1399,26 @@
         <v>9.1080466142032246E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9" s="11">
         <v>0.7</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="11">
         <v>0.2</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="11">
         <v>1.571</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="11">
         <v>1.571</v>
       </c>
-      <c r="E9" s="28">
-        <v>0</v>
-      </c>
-      <c r="F9" s="28">
-        <v>0</v>
-      </c>
-      <c r="G9" s="28">
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
         <v>0</v>
       </c>
       <c r="H9" s="9">
@@ -1484,26 +1482,26 @@
         <v>0.10715854673635526</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" s="11">
         <v>0.7</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="11">
         <v>0.06</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="11">
         <v>3.665</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="11">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E10" s="28">
-        <v>0</v>
-      </c>
-      <c r="F10" s="28">
-        <v>0</v>
-      </c>
-      <c r="G10" s="28">
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
         <v>0</v>
       </c>
       <c r="H10" s="9">
@@ -1567,26 +1565,26 @@
         <v>3.3466802983233901E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11" s="11">
         <v>0.6</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="11">
         <v>0.1</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="11">
         <v>3.665</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="11">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E11" s="28">
-        <v>0</v>
-      </c>
-      <c r="F11" s="28">
-        <v>0</v>
-      </c>
-      <c r="G11" s="28">
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
         <v>0</v>
       </c>
       <c r="H11" s="9">
@@ -1650,26 +1648,26 @@
         <v>1.5558310962285327E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12" s="11">
         <v>0.8</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="11">
         <v>0.18</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="11">
         <v>3.665</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="11">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="11">
         <v>1.4</v>
       </c>
-      <c r="F12" s="28">
-        <v>0</v>
-      </c>
-      <c r="G12" s="28">
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
         <v>0</v>
       </c>
       <c r="H12" s="9">
@@ -1733,26 +1731,26 @@
         <v>2.9085556228708065E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
         <v>0.4</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="11">
         <v>0.2</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="11">
         <v>3.665</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="11">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="11">
         <v>1.4</v>
       </c>
-      <c r="F13" s="28">
-        <v>0</v>
-      </c>
-      <c r="G13" s="28">
+      <c r="F13" s="11">
+        <v>0</v>
+      </c>
+      <c r="G13" s="11">
         <v>0</v>
       </c>
       <c r="H13" s="9">
@@ -1816,26 +1814,26 @@
         <v>3.7628630027377041E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
         <v>0.4</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="11">
         <v>0.1</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="11">
         <v>3.665</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="11">
         <v>1.571</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="11">
         <v>1.4</v>
       </c>
-      <c r="F14" s="28">
-        <v>0</v>
-      </c>
-      <c r="G14" s="28">
+      <c r="F14" s="11">
+        <v>0</v>
+      </c>
+      <c r="G14" s="11">
         <v>0</v>
       </c>
       <c r="H14" s="9">
@@ -1899,26 +1897,26 @@
         <v>3.8358183479932639E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="28">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
         <v>0.7</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="11">
         <v>0.1</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="11">
         <v>3.665</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="11">
         <v>1.571</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="11">
         <v>1.4</v>
       </c>
-      <c r="F15" s="28">
-        <v>0</v>
-      </c>
-      <c r="G15" s="28">
+      <c r="F15" s="11">
+        <v>0</v>
+      </c>
+      <c r="G15" s="11">
         <v>0</v>
       </c>
       <c r="H15" s="9">
@@ -1982,26 +1980,26 @@
         <v>2.2424507352374223E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16" s="11">
         <v>0.4</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="11">
         <v>0.16</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="11">
         <v>3.665</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="11">
         <v>1.571</v>
       </c>
-      <c r="E16" s="28">
-        <v>0</v>
-      </c>
-      <c r="F16" s="28">
-        <v>0</v>
-      </c>
-      <c r="G16" s="28">
+      <c r="E16" s="11">
+        <v>0</v>
+      </c>
+      <c r="F16" s="11">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11">
         <v>0</v>
       </c>
       <c r="H16" s="9">
@@ -2065,26 +2063,26 @@
         <v>3.7839914167488053E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="28">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
         <v>0.3</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="11">
         <v>0.18</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="11">
         <v>3.665</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="11">
         <v>1.571</v>
       </c>
-      <c r="E17" s="28">
-        <v>0</v>
-      </c>
-      <c r="F17" s="28">
-        <v>0</v>
-      </c>
-      <c r="G17" s="28">
+      <c r="E17" s="11">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11">
         <v>0</v>
       </c>
       <c r="H17" s="9">
@@ -2163,38 +2161,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D6F75F-00D5-499A-8B94-C01DFDD9DEC2}">
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
       <c r="H1" s="23" t="s">
         <v>6</v>
       </c>
@@ -2203,26 +2201,26 @@
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
       <c r="M1" s="23"/>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
       <c r="S1" s="24" t="s">
         <v>15</v>
       </c>
       <c r="T1" s="24"/>
       <c r="U1" s="24"/>
       <c r="V1" s="6"/>
-      <c r="W1" s="22" t="s">
+      <c r="W1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-    </row>
-    <row r="2" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2302,7 +2300,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <f>'Proximal Validation (single)'!A3</f>
         <v>0.3</v>
@@ -2403,7 +2401,7 @@
         <v>7.3272113589242058E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <f>'Proximal Validation (single)'!A4</f>
         <v>0.4</v>
@@ -2496,7 +2494,7 @@
         <v>4.1981828646667356</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <f>'Proximal Validation (single)'!A5</f>
         <v>0.6</v>
@@ -2581,7 +2579,7 @@
         <v>6.5729964811200414E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <f>'Proximal Validation (single)'!A6</f>
         <v>0.4</v>
@@ -2666,7 +2664,7 @@
         <v>1.5752653908777559E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <f>'Proximal Validation (single)'!A7</f>
         <v>0.8</v>
@@ -2751,7 +2749,7 @@
         <v>2.5383869340993792E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <f>'Proximal Validation (single)'!A8</f>
         <v>0.7</v>
@@ -2836,7 +2834,7 @@
         <v>1.5214757044127447E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <f>'Proximal Validation (single)'!A9</f>
         <v>0.7</v>
@@ -2921,7 +2919,7 @@
         <v>0.38952622811077386</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <f>'Proximal Validation (single)'!A10</f>
         <v>0.7</v>
@@ -3006,7 +3004,7 @@
         <v>2.7153534046437833E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <f>'Proximal Validation (single)'!A11</f>
         <v>0.6</v>
@@ -3091,7 +3089,7 @@
         <v>3.0792119452061173E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <f>'Proximal Validation (single)'!A12</f>
         <v>0.8</v>
@@ -3176,7 +3174,7 @@
         <v>0.19969441877939731</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <f>'Proximal Validation (single)'!A13</f>
         <v>0.4</v>
@@ -3261,7 +3259,7 @@
         <v>2.8395849857377753E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <f>'Proximal Validation (single)'!A14</f>
         <v>0.4</v>
@@ -3346,7 +3344,7 @@
         <v>4.1824823999520699E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <f>'Proximal Validation (single)'!A15</f>
         <v>0.7</v>
@@ -3431,7 +3429,7 @@
         <v>1.6827968094608403E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <f>'Proximal Validation (single)'!A16</f>
         <v>0.4</v>
@@ -3516,7 +3514,7 @@
         <v>1.4951456531285379E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <f>'Proximal Validation (single)'!A17</f>
         <v>0.3</v>
@@ -3617,38 +3615,38 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2528D5F-5B80-4411-8C57-013C25829219}">
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
       <c r="H1" s="23" t="s">
         <v>6</v>
       </c>
@@ -3657,26 +3655,26 @@
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
       <c r="M1" s="23"/>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
       <c r="S1" s="24" t="s">
         <v>15</v>
       </c>
       <c r="T1" s="24"/>
       <c r="U1" s="24"/>
       <c r="V1" s="6"/>
-      <c r="W1" s="22" t="s">
+      <c r="W1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-    </row>
-    <row r="2" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3756,7 +3754,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <f>'Proximal Validation (single)'!A3</f>
         <v>0.3</v>
@@ -3809,45 +3807,55 @@
         <f>'Proximal Validation (single)'!M3</f>
         <v>0.203822165727615</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="10"/>
+      <c r="N3" s="9">
+        <v>0.25176585675542784</v>
+      </c>
+      <c r="O3" s="9">
+        <v>7.7409627193909369E-2</v>
+      </c>
+      <c r="P3" s="9">
+        <v>1.6621857158434452</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0.89914821498112374</v>
+      </c>
+      <c r="R3" s="10">
+        <v>5.4458069220912406E-7</v>
+      </c>
       <c r="S3" s="8">
         <f>ABS(N3-A3)</f>
-        <v>0.3</v>
+        <v>4.8234143244572147E-2</v>
       </c>
       <c r="T3" s="8">
         <f t="shared" ref="T3:V17" si="0">ABS(O3-B3)</f>
-        <v>0.08</v>
+        <v>2.5903728060906323E-3</v>
       </c>
       <c r="U3" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>9.1185715843445259E-2</v>
       </c>
       <c r="V3" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
+        <v>0.11414821498112371</v>
       </c>
       <c r="W3" s="9">
         <f>AVERAGE(S3:S17)</f>
-        <v>0.54666666666666675</v>
+        <v>6.5696993611092061E-2</v>
       </c>
       <c r="X3" s="9">
         <f t="shared" ref="X3:Z3" si="1">AVERAGE(T3:T17)</f>
-        <v>0.13066666666666668</v>
+        <v>4.7584855273717079E-2</v>
       </c>
       <c r="Y3" s="9">
         <f>AVERAGE(U3:U17)</f>
-        <v>2.6877999999999997</v>
+        <v>0.34748627341881633</v>
       </c>
       <c r="Z3" s="9">
         <f t="shared" si="1"/>
-        <v>1.2042000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.26805843157632592</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <f>'Proximal Validation (single)'!A4</f>
         <v>0.4</v>
@@ -3900,37 +3908,47 @@
         <f>'Proximal Validation (single)'!M4</f>
         <v>0.30656093358993503</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="10"/>
+      <c r="N4" s="9">
+        <v>0.35629399825604641</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0.13471832852894311</v>
+      </c>
+      <c r="P4" s="9">
+        <v>1.5669433477186665</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0.85247017156916194</v>
+      </c>
+      <c r="R4" s="10">
+        <v>2.3890165641817172E-7</v>
+      </c>
       <c r="S4" s="8">
         <f t="shared" ref="S4:S17" si="2">ABS(N4-A4)</f>
-        <v>0.4</v>
+        <v>4.3706001743953615E-2</v>
       </c>
       <c r="T4" s="8">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>5.2816714710569035E-3</v>
       </c>
       <c r="U4" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>4.0566522813334505E-3</v>
       </c>
       <c r="V4" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
+        <v>6.7470171569161907E-2</v>
       </c>
       <c r="Y4">
         <f>DEGREES(Y3)</f>
-        <v>153.99959617526267</v>
+        <v>19.90949690562714</v>
       </c>
       <c r="Z4">
         <f>DEGREES(Z3)</f>
-        <v>68.995577689653743</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+        <v>15.358616792219834</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <f>'Proximal Validation (single)'!A5</f>
         <v>0.6</v>
@@ -3983,29 +4001,39 @@
         <f>'Proximal Validation (single)'!M5</f>
         <v>0.55316102504730202</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="10"/>
+      <c r="N5" s="9">
+        <v>0.57507826618722557</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0.14980258799311363</v>
+      </c>
+      <c r="P5" s="9">
+        <v>1.7240415983983191</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0.92934946998099011</v>
+      </c>
+      <c r="R5" s="10">
+        <v>1.5237257343147551E-5</v>
+      </c>
       <c r="S5" s="8">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>2.4921733812774405E-2</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>1.0197412006886369E-2</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>0.1530415983983191</v>
       </c>
       <c r="V5" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.14434946998099007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <f>'Proximal Validation (single)'!A6</f>
         <v>0.4</v>
@@ -4058,29 +4086,39 @@
         <f>'Proximal Validation (single)'!M6</f>
         <v>0.35301661491393999</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="10"/>
+      <c r="N6" s="9">
+        <v>0.36654435935139396</v>
+      </c>
+      <c r="O6" s="9">
+        <v>6.3887069546794129E-2</v>
+      </c>
+      <c r="P6" s="9">
+        <v>1.5993330077825643</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>1.5395564343121335</v>
+      </c>
+      <c r="R6" s="10">
+        <v>1.2746013392816786E-6</v>
+      </c>
       <c r="S6" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>3.3455640648606066E-2</v>
       </c>
       <c r="T6" s="8">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>3.8870695467941307E-3</v>
       </c>
       <c r="U6" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>2.8333007782564312E-2</v>
       </c>
       <c r="V6" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3.1443565687866437E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <f>'Proximal Validation (single)'!A7</f>
         <v>0.8</v>
@@ -4133,29 +4171,39 @@
         <f>'Proximal Validation (single)'!M7</f>
         <v>0.66739636659622203</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="10"/>
+      <c r="N7" s="9">
+        <v>0.70592240299008657</v>
+      </c>
+      <c r="O7" s="9">
+        <v>8.275552128522895E-2</v>
+      </c>
+      <c r="P7" s="9">
+        <v>1.5747160346001037</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>1.5451556337327086</v>
+      </c>
+      <c r="R7" s="10">
+        <v>1.3697771643074497E-7</v>
+      </c>
       <c r="S7" s="8">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>9.4077597009913472E-2</v>
       </c>
       <c r="T7" s="8">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>2.7555212852289485E-3</v>
       </c>
       <c r="U7" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>3.7160346001037237E-3</v>
       </c>
       <c r="V7" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2.5844366267291363E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <f>'Proximal Validation (single)'!A8</f>
         <v>0.7</v>
@@ -4208,29 +4256,39 @@
         <f>'Proximal Validation (single)'!M8</f>
         <v>0.32599642872810403</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="10"/>
+      <c r="N8" s="9">
+        <v>0.54703734660826808</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0.19786414298364685</v>
+      </c>
+      <c r="P8" s="9">
+        <v>1.6742422185830164</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>1.3713390827862426</v>
+      </c>
+      <c r="R8" s="10">
+        <v>5.4245097123915403E-5</v>
+      </c>
       <c r="S8" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>0.15296265339173187</v>
       </c>
       <c r="T8" s="8">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>3.7864142983646848E-2</v>
       </c>
       <c r="U8" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>0.10324221858301641</v>
       </c>
       <c r="V8" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.19966091721375734</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <f>'Proximal Validation (single)'!A9</f>
         <v>0.7</v>
@@ -4283,29 +4341,39 @@
         <f>'Proximal Validation (single)'!M9</f>
         <v>0.10576334595680199</v>
       </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="10"/>
+      <c r="N9" s="9">
+        <v>0.47548452235230187</v>
+      </c>
+      <c r="O9" s="9">
+        <v>4.437244102470661E-2</v>
+      </c>
+      <c r="P9" s="9">
+        <v>6.2831853071795862</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>3.1061528590975596</v>
+      </c>
+      <c r="R9" s="10">
+        <v>2.6238455690372735E-2</v>
+      </c>
       <c r="S9" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>0.22451547764769808</v>
       </c>
       <c r="T9" s="8">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.1556275589752934</v>
       </c>
       <c r="U9" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>4.7121853071795865</v>
       </c>
       <c r="V9" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1.5351528590975596</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <f>'Proximal Validation (single)'!A10</f>
         <v>0.7</v>
@@ -4358,29 +4426,39 @@
         <f>'Proximal Validation (single)'!M10</f>
         <v>-0.30146327614784202</v>
       </c>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="10"/>
+      <c r="N10" s="9">
+        <v>0.75074610793503893</v>
+      </c>
+      <c r="O10" s="9">
+        <v>1.3431835239219408E-2</v>
+      </c>
+      <c r="P10" s="9">
+        <v>3.6416787591438236</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>1.0526974488868213</v>
+      </c>
+      <c r="R10" s="10">
+        <v>2.2497535216449213E-4</v>
+      </c>
       <c r="S10" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>5.0746107935038975E-2</v>
       </c>
       <c r="T10" s="8">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>4.6568164760780587E-2</v>
       </c>
       <c r="U10" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>2.3321240856176484E-2</v>
       </c>
       <c r="V10" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.26769744888682123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <f>'Proximal Validation (single)'!A11</f>
         <v>0.6</v>
@@ -4433,29 +4511,39 @@
         <f>'Proximal Validation (single)'!M11</f>
         <v>-0.25065129995346103</v>
       </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="10"/>
+      <c r="N11" s="9">
+        <v>0.5970359596445165</v>
+      </c>
+      <c r="O11" s="9">
+        <v>3.7515951981484073E-2</v>
+      </c>
+      <c r="P11" s="9">
+        <v>3.648642710341881</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>1.0852176234594224</v>
+      </c>
+      <c r="R11" s="10">
+        <v>2.3717877448000015E-4</v>
+      </c>
       <c r="S11" s="8">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>2.9640403554834771E-3</v>
       </c>
       <c r="T11" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>6.2484048018515932E-2</v>
       </c>
       <c r="U11" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.6357289658119001E-2</v>
       </c>
       <c r="V11" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.30021762345942238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <f>'Proximal Validation (single)'!A12</f>
         <v>0.8</v>
@@ -4508,29 +4596,39 @@
         <f>'Proximal Validation (single)'!M12</f>
         <v>-0.37070235610008201</v>
       </c>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="10"/>
+      <c r="N12" s="9">
+        <v>0.79793926075448995</v>
+      </c>
+      <c r="O12" s="9">
+        <v>6.9288764828584579E-2</v>
+      </c>
+      <c r="P12" s="9">
+        <v>3.6709044520221457</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>1.1958102569293623</v>
+      </c>
+      <c r="R12" s="10">
+        <v>8.0700200924051484E-4</v>
+      </c>
       <c r="S12" s="8">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>2.0607392455100904E-3</v>
       </c>
       <c r="T12" s="8">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.11071123517141541</v>
       </c>
       <c r="U12" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>5.9044520221456231E-3</v>
       </c>
       <c r="V12" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.41081025692936224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <f>'Proximal Validation (single)'!A13</f>
         <v>0.4</v>
@@ -4583,29 +4681,39 @@
         <f>'Proximal Validation (single)'!M13</f>
         <v>-0.14198835194110901</v>
       </c>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="10"/>
+      <c r="N13" s="9">
+        <v>0.32489071306931105</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0.11087241142802345</v>
+      </c>
+      <c r="P13" s="9">
+        <v>3.6785347202142877</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>1.0638317011350482</v>
+      </c>
+      <c r="R13" s="10">
+        <v>1.9777367671421357E-4</v>
+      </c>
       <c r="S13" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>7.5109286930688968E-2</v>
       </c>
       <c r="T13" s="8">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>8.9127588571976557E-2</v>
       </c>
       <c r="U13" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.3534720214287699E-2</v>
       </c>
       <c r="V13" s="8">
         <f t="shared" si="0"/>
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.27883170113504818</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <f>'Proximal Validation (single)'!A14</f>
         <v>0.4</v>
@@ -4658,29 +4766,39 @@
         <f>'Proximal Validation (single)'!M14</f>
         <v>-0.16083618998527499</v>
       </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="10"/>
+      <c r="N14" s="9">
+        <v>0.34416239594645848</v>
+      </c>
+      <c r="O14" s="9">
+        <v>4.9986407190874278E-2</v>
+      </c>
+      <c r="P14" s="9">
+        <v>3.6510423656869309</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>1.6119724393674215</v>
+      </c>
+      <c r="R14" s="10">
+        <v>1.1816515120822258E-4</v>
+      </c>
       <c r="S14" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>5.5837604053541545E-2</v>
       </c>
       <c r="T14" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>5.0013592809125727E-2</v>
       </c>
       <c r="U14" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.3957634313069178E-2</v>
       </c>
       <c r="V14" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.0972439367421565E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <f>'Proximal Validation (single)'!A15</f>
         <v>0.7</v>
@@ -4733,29 +4851,39 @@
         <f>'Proximal Validation (single)'!M15</f>
         <v>-0.318100035190582</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="10"/>
+      <c r="N15" s="9">
+        <v>0.69544594524453762</v>
+      </c>
+      <c r="O15" s="9">
+        <v>5.2557298783545314E-2</v>
+      </c>
+      <c r="P15" s="9">
+        <v>3.6511753801642577</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>1.7445398991530929</v>
+      </c>
+      <c r="R15" s="10">
+        <v>4.921856608278149E-4</v>
+      </c>
       <c r="S15" s="8">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>4.5540547554623334E-3</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>4.7442701216454691E-2</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>1.3824619835742347E-2</v>
       </c>
       <c r="V15" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.17353989915309298</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <f>'Proximal Validation (single)'!A16</f>
         <v>0.4</v>
@@ -4808,29 +4936,39 @@
         <f>'Proximal Validation (single)'!M16</f>
         <v>-0.13795974850654599</v>
       </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="10"/>
+      <c r="N16" s="9">
+        <v>0.31412690457687131</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0.11322165068839618</v>
+      </c>
+      <c r="P16" s="9">
+        <v>3.6722292682763</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>1.8008750431539418</v>
+      </c>
+      <c r="R16" s="10">
+        <v>1.7736969670218347E-4</v>
+      </c>
       <c r="S16" s="8">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>8.5873095423128709E-2</v>
       </c>
       <c r="T16" s="8">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>4.6778349311603823E-2</v>
       </c>
       <c r="U16" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>7.2292682762999938E-3</v>
       </c>
       <c r="V16" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.2298750431539418</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <f>'Proximal Validation (single)'!A17</f>
         <v>0.3</v>
@@ -4883,26 +5021,36 @@
         <f>'Proximal Validation (single)'!M17</f>
         <v>-9.7047880291938796E-2</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="10"/>
+      <c r="N17" s="9">
+        <v>0.21356327203172287</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0.13755659982911375</v>
+      </c>
+      <c r="P17" s="9">
+        <v>3.6874043414380351</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>1.7718624967620284</v>
+      </c>
+      <c r="R17" s="10">
+        <v>1.017634987128293E-4</v>
+      </c>
       <c r="S17" s="8">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>8.6436727968277116E-2</v>
       </c>
       <c r="T17" s="8">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>4.2443400170886242E-2</v>
       </c>
       <c r="U17" s="8">
         <f t="shared" si="0"/>
-        <v>3.665</v>
+        <v>2.2404341438035047E-2</v>
       </c>
       <c r="V17" s="8">
         <f t="shared" si="0"/>
-        <v>1.571</v>
+        <v>0.2008624967620285</v>
       </c>
     </row>
   </sheetData>
@@ -4919,29 +5067,1928 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57CC1EEA-6489-4659-B29B-A96532753335}">
+  <dimension ref="A1:Z17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+    </row>
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <f>'Proximal Validation (single)'!A3</f>
+        <v>0.3</v>
+      </c>
+      <c r="B3" s="9">
+        <f>'Proximal Validation (single)'!B3</f>
+        <v>0.08</v>
+      </c>
+      <c r="C3" s="9">
+        <f>'Proximal Validation (single)'!C3</f>
+        <v>1.571</v>
+      </c>
+      <c r="D3" s="9">
+        <f>'Proximal Validation (single)'!D3</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E3" s="9">
+        <f>'Proximal Validation (single)'!E3</f>
+        <v>1.4</v>
+      </c>
+      <c r="F3" s="9">
+        <f>'Proximal Validation (single)'!F3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="9">
+        <f>'Proximal Validation (single)'!G3</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <f>'Proximal Validation (single)'!H3</f>
+        <v>8.3457410801202102E-4</v>
+      </c>
+      <c r="I3" s="9">
+        <f>'Proximal Validation (single)'!I3</f>
+        <v>-3.4524299204349497E-2</v>
+      </c>
+      <c r="J3" s="9">
+        <f>'Proximal Validation (single)'!J3</f>
+        <v>-1.46811630111188E-3</v>
+      </c>
+      <c r="K3" s="9">
+        <f>'Proximal Validation (single)'!K3</f>
+        <v>0.179403036832809</v>
+      </c>
+      <c r="L3" s="9">
+        <f>'Proximal Validation (single)'!L3</f>
+        <v>-7.5630694627761797E-3</v>
+      </c>
+      <c r="M3" s="9">
+        <f>'Proximal Validation (single)'!M3</f>
+        <v>0.203822165727615</v>
+      </c>
+      <c r="N3" s="9">
+        <v>0.22991720198235813</v>
+      </c>
+      <c r="O3" s="9">
+        <v>6.2828243105734566E-2</v>
+      </c>
+      <c r="P3" s="9">
+        <v>1.5686685201921333</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>1.2224638893163442</v>
+      </c>
+      <c r="R3" s="10">
+        <v>5.2882092668436482E-4</v>
+      </c>
+      <c r="S3" s="8">
+        <f>ABS(N3-A3)</f>
+        <v>7.0082798017641862E-2</v>
+      </c>
+      <c r="T3" s="8">
+        <f t="shared" ref="T3:V17" si="0">ABS(O3-B3)</f>
+        <v>1.7171756894265436E-2</v>
+      </c>
+      <c r="U3" s="8">
+        <f t="shared" si="0"/>
+        <v>2.3314798078666321E-3</v>
+      </c>
+      <c r="V3" s="8">
+        <f t="shared" si="0"/>
+        <v>0.43746388931634417</v>
+      </c>
+      <c r="W3" s="9">
+        <f>AVERAGE(S3:S17)</f>
+        <v>4.3251297317164476E-2</v>
+      </c>
+      <c r="X3" s="9">
+        <f t="shared" ref="X3:Z3" si="1">AVERAGE(T3:T17)</f>
+        <v>3.7362062394773896E-2</v>
+      </c>
+      <c r="Y3" s="9">
+        <f>AVERAGE(U3:U17)</f>
+        <v>0.34525671127966362</v>
+      </c>
+      <c r="Z3" s="9">
+        <f t="shared" si="1"/>
+        <v>0.31331560494980876</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A4" s="9">
+        <f>'Proximal Validation (single)'!A4</f>
+        <v>0.4</v>
+      </c>
+      <c r="B4" s="9">
+        <f>'Proximal Validation (single)'!B4</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C4" s="9">
+        <f>'Proximal Validation (single)'!C4</f>
+        <v>1.571</v>
+      </c>
+      <c r="D4" s="9">
+        <f>'Proximal Validation (single)'!D4</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E4" s="9">
+        <f>'Proximal Validation (single)'!E4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <f>'Proximal Validation (single)'!F4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="9">
+        <f>'Proximal Validation (single)'!G4</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <f>'Proximal Validation (single)'!H4</f>
+        <v>-8.0810196232050701E-4</v>
+      </c>
+      <c r="I4" s="9">
+        <f>'Proximal Validation (single)'!I4</f>
+        <v>-6.6743046045303303E-2</v>
+      </c>
+      <c r="J4" s="9">
+        <f>'Proximal Validation (single)'!J4</f>
+        <v>4.4342974433675398E-4</v>
+      </c>
+      <c r="K4" s="9">
+        <f>'Proximal Validation (single)'!K4</f>
+        <v>0.21195751428604101</v>
+      </c>
+      <c r="L4" s="9">
+        <f>'Proximal Validation (single)'!L4</f>
+        <v>1.1818818747997299E-3</v>
+      </c>
+      <c r="M4" s="9">
+        <f>'Proximal Validation (single)'!M4</f>
+        <v>0.30656093358993503</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0.33788822406816815</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0.11871880754932461</v>
+      </c>
+      <c r="P4" s="9">
+        <v>1.5324973262704957</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>1.0787440988543255</v>
+      </c>
+      <c r="R4" s="10">
+        <v>5.6166663921947536E-4</v>
+      </c>
+      <c r="S4" s="8">
+        <f t="shared" ref="S4:S17" si="2">ABS(N4-A4)</f>
+        <v>6.211177593183187E-2</v>
+      </c>
+      <c r="T4" s="8">
+        <f t="shared" si="0"/>
+        <v>2.1281192450675404E-2</v>
+      </c>
+      <c r="U4" s="8">
+        <f t="shared" si="0"/>
+        <v>3.8502673729504222E-2</v>
+      </c>
+      <c r="V4" s="8">
+        <f t="shared" si="0"/>
+        <v>0.29374409885432551</v>
+      </c>
+      <c r="Y4">
+        <f>DEGREES(Y3)</f>
+        <v>19.781752404891531</v>
+      </c>
+      <c r="Z4">
+        <f>DEGREES(Z3)</f>
+        <v>17.951661819212248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
+        <f>'Proximal Validation (single)'!A5</f>
+        <v>0.6</v>
+      </c>
+      <c r="B5" s="9">
+        <f>'Proximal Validation (single)'!B5</f>
+        <v>0.16</v>
+      </c>
+      <c r="C5" s="9">
+        <f>'Proximal Validation (single)'!C5</f>
+        <v>1.571</v>
+      </c>
+      <c r="D5" s="9">
+        <f>'Proximal Validation (single)'!D5</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E5" s="9">
+        <f>'Proximal Validation (single)'!E5</f>
+        <v>1.4</v>
+      </c>
+      <c r="F5" s="9">
+        <f>'Proximal Validation (single)'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <f>'Proximal Validation (single)'!G5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <f>'Proximal Validation (single)'!H5</f>
+        <v>7.8557301312684995E-3</v>
+      </c>
+      <c r="I5" s="9">
+        <f>'Proximal Validation (single)'!I5</f>
+        <v>-0.127810284495354</v>
+      </c>
+      <c r="J5" s="9">
+        <f>'Proximal Validation (single)'!J5</f>
+        <v>-1.16112818941474E-2</v>
+      </c>
+      <c r="K5" s="9">
+        <f>'Proximal Validation (single)'!K5</f>
+        <v>2.8561159968376201E-2</v>
+      </c>
+      <c r="L5" s="9">
+        <f>'Proximal Validation (single)'!L5</f>
+        <v>-4.7612398862838697E-2</v>
+      </c>
+      <c r="M5" s="9">
+        <f>'Proximal Validation (single)'!M5</f>
+        <v>0.55316102504730202</v>
+      </c>
+      <c r="N5" s="9">
+        <v>0.57870479017900989</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0.13712967895377676</v>
+      </c>
+      <c r="P5" s="9">
+        <v>1.6655657432120243</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>1.1569604667416944</v>
+      </c>
+      <c r="R5" s="10">
+        <v>5.9228286510050303E-4</v>
+      </c>
+      <c r="S5" s="8">
+        <f t="shared" si="2"/>
+        <v>2.1295209820990091E-2</v>
+      </c>
+      <c r="T5" s="8">
+        <f t="shared" si="0"/>
+        <v>2.2870321046223246E-2</v>
+      </c>
+      <c r="U5" s="8">
+        <f t="shared" si="0"/>
+        <v>9.4565743212024378E-2</v>
+      </c>
+      <c r="V5" s="8">
+        <f t="shared" si="0"/>
+        <v>0.37196046674169436</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
+        <f>'Proximal Validation (single)'!A6</f>
+        <v>0.4</v>
+      </c>
+      <c r="B6" s="9">
+        <f>'Proximal Validation (single)'!B6</f>
+        <v>0.06</v>
+      </c>
+      <c r="C6" s="9">
+        <f>'Proximal Validation (single)'!C6</f>
+        <v>1.571</v>
+      </c>
+      <c r="D6" s="9">
+        <f>'Proximal Validation (single)'!D6</f>
+        <v>1.571</v>
+      </c>
+      <c r="E6" s="9">
+        <f>'Proximal Validation (single)'!E6</f>
+        <v>1.4</v>
+      </c>
+      <c r="F6" s="9">
+        <f>'Proximal Validation (single)'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <f>'Proximal Validation (single)'!G6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <f>'Proximal Validation (single)'!H6</f>
+        <v>1.1252735275775201E-3</v>
+      </c>
+      <c r="I6" s="9">
+        <f>'Proximal Validation (single)'!I6</f>
+        <v>-5.59809319674969E-2</v>
+      </c>
+      <c r="J6" s="9">
+        <f>'Proximal Validation (single)'!J6</f>
+        <v>-7.4938102625310399E-4</v>
+      </c>
+      <c r="K6" s="9">
+        <f>'Proximal Validation (single)'!K6</f>
+        <v>-3.5423979163169902E-2</v>
+      </c>
+      <c r="L6" s="9">
+        <f>'Proximal Validation (single)'!L6</f>
+        <v>-1.04948431253433E-2</v>
+      </c>
+      <c r="M6" s="9">
+        <f>'Proximal Validation (single)'!M6</f>
+        <v>0.35301661491393999</v>
+      </c>
+      <c r="N6" s="9">
+        <v>0.40103931158116202</v>
+      </c>
+      <c r="O6" s="9">
+        <v>5.6609959262260971E-2</v>
+      </c>
+      <c r="P6" s="9">
+        <v>1.5466366345774443</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>1.8718423198094816</v>
+      </c>
+      <c r="R6" s="10">
+        <v>4.934855882077889E-4</v>
+      </c>
+      <c r="S6" s="8">
+        <f t="shared" si="2"/>
+        <v>1.0393115811619946E-3</v>
+      </c>
+      <c r="T6" s="8">
+        <f t="shared" si="0"/>
+        <v>3.3900407377390265E-3</v>
+      </c>
+      <c r="U6" s="8">
+        <f t="shared" si="0"/>
+        <v>2.4363365422555683E-2</v>
+      </c>
+      <c r="V6" s="8">
+        <f t="shared" si="0"/>
+        <v>0.30084231980948162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A7" s="9">
+        <f>'Proximal Validation (single)'!A7</f>
+        <v>0.8</v>
+      </c>
+      <c r="B7" s="9">
+        <f>'Proximal Validation (single)'!B7</f>
+        <v>0.08</v>
+      </c>
+      <c r="C7" s="9">
+        <f>'Proximal Validation (single)'!C7</f>
+        <v>1.571</v>
+      </c>
+      <c r="D7" s="9">
+        <f>'Proximal Validation (single)'!D7</f>
+        <v>1.571</v>
+      </c>
+      <c r="E7" s="9">
+        <f>'Proximal Validation (single)'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <f>'Proximal Validation (single)'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <f>'Proximal Validation (single)'!G7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <f>'Proximal Validation (single)'!H7</f>
+        <v>-5.5839424021542105E-4</v>
+      </c>
+      <c r="I7" s="9">
+        <f>'Proximal Validation (single)'!I7</f>
+        <v>-0.11975701153278399</v>
+      </c>
+      <c r="J7" s="9">
+        <f>'Proximal Validation (single)'!J7</f>
+        <v>-9.9074037279933691E-4</v>
+      </c>
+      <c r="K7" s="9">
+        <f>'Proximal Validation (single)'!K7</f>
+        <v>-0.19020733237266499</v>
+      </c>
+      <c r="L7" s="9">
+        <f>'Proximal Validation (single)'!L7</f>
+        <v>-2.60122120380402E-3</v>
+      </c>
+      <c r="M7" s="9">
+        <f>'Proximal Validation (single)'!M7</f>
+        <v>0.66739636659622203</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0.75103386657084459</v>
+      </c>
+      <c r="O7" s="9">
+        <v>7.9849433746575896E-2</v>
+      </c>
+      <c r="P7" s="9">
+        <v>1.557447002876535</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>1.7690879529068655</v>
+      </c>
+      <c r="R7" s="10">
+        <v>5.7315130600234037E-4</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" si="2"/>
+        <v>4.8966133429155456E-2</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" si="0"/>
+        <v>1.505662534241059E-4</v>
+      </c>
+      <c r="U7" s="8">
+        <f t="shared" si="0"/>
+        <v>1.3552997123464916E-2</v>
+      </c>
+      <c r="V7" s="8">
+        <f t="shared" si="0"/>
+        <v>0.19808795290686554</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A8" s="9">
+        <f>'Proximal Validation (single)'!A8</f>
+        <v>0.7</v>
+      </c>
+      <c r="B8" s="9">
+        <f>'Proximal Validation (single)'!B8</f>
+        <v>0.16</v>
+      </c>
+      <c r="C8" s="9">
+        <f>'Proximal Validation (single)'!C8</f>
+        <v>1.571</v>
+      </c>
+      <c r="D8" s="9">
+        <f>'Proximal Validation (single)'!D8</f>
+        <v>1.571</v>
+      </c>
+      <c r="E8" s="9">
+        <f>'Proximal Validation (single)'!E8</f>
+        <v>1.4</v>
+      </c>
+      <c r="F8" s="9">
+        <f>'Proximal Validation (single)'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <f>'Proximal Validation (single)'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <f>'Proximal Validation (single)'!H8</f>
+        <v>1.04370433837175E-2</v>
+      </c>
+      <c r="I8" s="9">
+        <f>'Proximal Validation (single)'!I8</f>
+        <v>-0.129757210612297</v>
+      </c>
+      <c r="J8" s="9">
+        <f>'Proximal Validation (single)'!J8</f>
+        <v>-7.3771281167864799E-3</v>
+      </c>
+      <c r="K8" s="9">
+        <f>'Proximal Validation (single)'!K8</f>
+        <v>-0.55726921558380105</v>
+      </c>
+      <c r="L8" s="9">
+        <f>'Proximal Validation (single)'!L8</f>
+        <v>-6.0898363590240499E-2</v>
+      </c>
+      <c r="M8" s="9">
+        <f>'Proximal Validation (single)'!M8</f>
+        <v>0.32599642872810403</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0.75929596541303868</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0.15276134375627007</v>
+      </c>
+      <c r="P8" s="9">
+        <v>1.5690939986378372</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>1.8052689531082284</v>
+      </c>
+      <c r="R8" s="10">
+        <v>5.7596021484972106E-4</v>
+      </c>
+      <c r="S8" s="8">
+        <f t="shared" si="2"/>
+        <v>5.929596541303872E-2</v>
+      </c>
+      <c r="T8" s="8">
+        <f t="shared" si="0"/>
+        <v>7.2386562437299351E-3</v>
+      </c>
+      <c r="U8" s="8">
+        <f t="shared" si="0"/>
+        <v>1.9060013621627903E-3</v>
+      </c>
+      <c r="V8" s="8">
+        <f t="shared" si="0"/>
+        <v>0.23426895310822848</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A9" s="9">
+        <f>'Proximal Validation (single)'!A9</f>
+        <v>0.7</v>
+      </c>
+      <c r="B9" s="9">
+        <f>'Proximal Validation (single)'!B9</f>
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="9">
+        <f>'Proximal Validation (single)'!C9</f>
+        <v>1.571</v>
+      </c>
+      <c r="D9" s="9">
+        <f>'Proximal Validation (single)'!D9</f>
+        <v>1.571</v>
+      </c>
+      <c r="E9" s="9">
+        <f>'Proximal Validation (single)'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <f>'Proximal Validation (single)'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <f>'Proximal Validation (single)'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <f>'Proximal Validation (single)'!H9</f>
+        <v>-5.38935419172049E-4</v>
+      </c>
+      <c r="I9" s="9">
+        <f>'Proximal Validation (single)'!I9</f>
+        <v>-0.118809439241886</v>
+      </c>
+      <c r="J9" s="9">
+        <f>'Proximal Validation (single)'!J9</f>
+        <v>3.4749228507280402E-3</v>
+      </c>
+      <c r="K9" s="9">
+        <f>'Proximal Validation (single)'!K9</f>
+        <v>-0.621493339538574</v>
+      </c>
+      <c r="L9" s="9">
+        <f>'Proximal Validation (single)'!L9</f>
+        <v>1.56053192913532E-2</v>
+      </c>
+      <c r="M9" s="9">
+        <f>'Proximal Validation (single)'!M9</f>
+        <v>0.10576334595680199</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0.73975760209672059</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="P9" s="9">
+        <v>6.2831853071795862</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>3.1019545458073381</v>
+      </c>
+      <c r="R9" s="10">
+        <v>2.969116230592083E-2</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" si="2"/>
+        <v>3.9757602096720634E-2</v>
+      </c>
+      <c r="T9" s="8">
+        <f t="shared" si="0"/>
+        <v>0.19</v>
+      </c>
+      <c r="U9" s="8">
+        <f t="shared" si="0"/>
+        <v>4.7121853071795865</v>
+      </c>
+      <c r="V9" s="8">
+        <f t="shared" si="0"/>
+        <v>1.5309545458073381</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A10" s="9">
+        <f>'Proximal Validation (single)'!A10</f>
+        <v>0.7</v>
+      </c>
+      <c r="B10" s="9">
+        <f>'Proximal Validation (single)'!B10</f>
+        <v>0.06</v>
+      </c>
+      <c r="C10" s="9">
+        <f>'Proximal Validation (single)'!C10</f>
+        <v>3.665</v>
+      </c>
+      <c r="D10" s="9">
+        <f>'Proximal Validation (single)'!D10</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E10" s="9">
+        <f>'Proximal Validation (single)'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <f>'Proximal Validation (single)'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <f>'Proximal Validation (single)'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <f>'Proximal Validation (single)'!H10</f>
+        <v>-7.8150304034352303E-4</v>
+      </c>
+      <c r="I10" s="9">
+        <f>'Proximal Validation (single)'!I10</f>
+        <v>4.4897478073835401E-2</v>
+      </c>
+      <c r="J10" s="9">
+        <f>'Proximal Validation (single)'!J10</f>
+        <v>-8.2051888108253507E-2</v>
+      </c>
+      <c r="K10" s="9">
+        <f>'Proximal Validation (single)'!K10</f>
+        <v>0.48326423764228799</v>
+      </c>
+      <c r="L10" s="9">
+        <f>'Proximal Validation (single)'!L10</f>
+        <v>-0.55701375007629395</v>
+      </c>
+      <c r="M10" s="9">
+        <f>'Proximal Validation (single)'!M10</f>
+        <v>-0.30146327614784202</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0.71244789726745184</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0.10288880986972568</v>
+      </c>
+      <c r="P10" s="9">
+        <v>3.6225652959424823</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0.76536292993431254</v>
+      </c>
+      <c r="R10" s="10">
+        <v>1.5835082342366457E-4</v>
+      </c>
+      <c r="S10" s="8">
+        <f t="shared" si="2"/>
+        <v>1.244789726745188E-2</v>
+      </c>
+      <c r="T10" s="8">
+        <f t="shared" si="0"/>
+        <v>4.288880986972568E-2</v>
+      </c>
+      <c r="U10" s="8">
+        <f t="shared" si="0"/>
+        <v>4.2434704057517703E-2</v>
+      </c>
+      <c r="V10" s="8">
+        <f t="shared" si="0"/>
+        <v>1.963707006568749E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11" s="9">
+        <f>'Proximal Validation (single)'!A11</f>
+        <v>0.6</v>
+      </c>
+      <c r="B11" s="9">
+        <f>'Proximal Validation (single)'!B11</f>
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="9">
+        <f>'Proximal Validation (single)'!C11</f>
+        <v>3.665</v>
+      </c>
+      <c r="D11" s="9">
+        <f>'Proximal Validation (single)'!D11</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E11" s="9">
+        <f>'Proximal Validation (single)'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <f>'Proximal Validation (single)'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <f>'Proximal Validation (single)'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <f>'Proximal Validation (single)'!H11</f>
+        <v>-4.8895599320530902E-4</v>
+      </c>
+      <c r="I11" s="9">
+        <f>'Proximal Validation (single)'!I11</f>
+        <v>4.6247739344835302E-2</v>
+      </c>
+      <c r="J11" s="9">
+        <f>'Proximal Validation (single)'!J11</f>
+        <v>-8.3231396973133101E-2</v>
+      </c>
+      <c r="K11" s="9">
+        <f>'Proximal Validation (single)'!K11</f>
+        <v>0.33926415443420399</v>
+      </c>
+      <c r="L11" s="9">
+        <f>'Proximal Validation (single)'!L11</f>
+        <v>-0.45690825581550598</v>
+      </c>
+      <c r="M11" s="9">
+        <f>'Proximal Validation (single)'!M11</f>
+        <v>-0.25065129995346103</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0.54621033698664978</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0.17200658051123363</v>
+      </c>
+      <c r="P11" s="9">
+        <v>3.62470965629536</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0.63513419296129725</v>
+      </c>
+      <c r="R11" s="10">
+        <v>1.4746021098091292E-4</v>
+      </c>
+      <c r="S11" s="8">
+        <f t="shared" si="2"/>
+        <v>5.3789663013350197E-2</v>
+      </c>
+      <c r="T11" s="8">
+        <f t="shared" si="0"/>
+        <v>7.2006580511233625E-2</v>
+      </c>
+      <c r="U11" s="8">
+        <f t="shared" si="0"/>
+        <v>4.0290343704640019E-2</v>
+      </c>
+      <c r="V11" s="8">
+        <f t="shared" si="0"/>
+        <v>0.14986580703870278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A12" s="9">
+        <f>'Proximal Validation (single)'!A12</f>
+        <v>0.8</v>
+      </c>
+      <c r="B12" s="9">
+        <f>'Proximal Validation (single)'!B12</f>
+        <v>0.18</v>
+      </c>
+      <c r="C12" s="9">
+        <f>'Proximal Validation (single)'!C12</f>
+        <v>3.665</v>
+      </c>
+      <c r="D12" s="9">
+        <f>'Proximal Validation (single)'!D12</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E12" s="9">
+        <f>'Proximal Validation (single)'!E12</f>
+        <v>1.4</v>
+      </c>
+      <c r="F12" s="9">
+        <f>'Proximal Validation (single)'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <f>'Proximal Validation (single)'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <f>'Proximal Validation (single)'!H12</f>
+        <v>1.7005717381834999E-3</v>
+      </c>
+      <c r="I12" s="9">
+        <f>'Proximal Validation (single)'!I12</f>
+        <v>8.4788650274276706E-2</v>
+      </c>
+      <c r="J12" s="9">
+        <f>'Proximal Validation (single)'!J12</f>
+        <v>-0.143600359559059</v>
+      </c>
+      <c r="K12" s="9">
+        <f>'Proximal Validation (single)'!K12</f>
+        <v>0.28701612353324901</v>
+      </c>
+      <c r="L12" s="9">
+        <f>'Proximal Validation (single)'!L12</f>
+        <v>-0.64443814754486095</v>
+      </c>
+      <c r="M12" s="9">
+        <f>'Proximal Validation (single)'!M12</f>
+        <v>-0.37070235610008201</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0.74323630116649275</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P12" s="9">
+        <v>3.6540069491101859</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0.64037324415779184</v>
+      </c>
+      <c r="R12" s="10">
+        <v>2.5763920067375202E-4</v>
+      </c>
+      <c r="S12" s="8">
+        <f t="shared" si="2"/>
+        <v>5.6763698833507292E-2</v>
+      </c>
+      <c r="T12" s="8">
+        <f t="shared" si="0"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="U12" s="8">
+        <f t="shared" si="0"/>
+        <v>1.0993050889814171E-2</v>
+      </c>
+      <c r="V12" s="8">
+        <f t="shared" si="0"/>
+        <v>0.14462675584220819</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13" s="9">
+        <f>'Proximal Validation (single)'!A13</f>
+        <v>0.4</v>
+      </c>
+      <c r="B13" s="9">
+        <f>'Proximal Validation (single)'!B13</f>
+        <v>0.2</v>
+      </c>
+      <c r="C13" s="9">
+        <f>'Proximal Validation (single)'!C13</f>
+        <v>3.665</v>
+      </c>
+      <c r="D13" s="9">
+        <f>'Proximal Validation (single)'!D13</f>
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E13" s="9">
+        <f>'Proximal Validation (single)'!E13</f>
+        <v>1.4</v>
+      </c>
+      <c r="F13" s="9">
+        <f>'Proximal Validation (single)'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <f>'Proximal Validation (single)'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <f>'Proximal Validation (single)'!H13</f>
+        <v>1.0739560239017001E-3</v>
+      </c>
+      <c r="I13" s="9">
+        <f>'Proximal Validation (single)'!I13</f>
+        <v>4.1172292083501802E-2</v>
+      </c>
+      <c r="J13" s="9">
+        <f>'Proximal Validation (single)'!J13</f>
+        <v>-6.7707680165767697E-2</v>
+      </c>
+      <c r="K13" s="9">
+        <f>'Proximal Validation (single)'!K13</f>
+        <v>0.187965422868729</v>
+      </c>
+      <c r="L13" s="9">
+        <f>'Proximal Validation (single)'!L13</f>
+        <v>-0.244067072868347</v>
+      </c>
+      <c r="M13" s="9">
+        <f>'Proximal Validation (single)'!M13</f>
+        <v>-0.14198835194110901</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0.27514846325161291</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P13" s="9">
+        <v>3.6389101868005804</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>1.0703872443459503</v>
+      </c>
+      <c r="R13" s="10">
+        <v>6.6616982525375171E-4</v>
+      </c>
+      <c r="S13" s="8">
+        <f t="shared" si="2"/>
+        <v>0.12485153674838712</v>
+      </c>
+      <c r="T13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="8">
+        <f t="shared" si="0"/>
+        <v>2.6089813199419609E-2</v>
+      </c>
+      <c r="V13" s="8">
+        <f t="shared" si="0"/>
+        <v>0.28538724434595031</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A14" s="9">
+        <f>'Proximal Validation (single)'!A14</f>
+        <v>0.4</v>
+      </c>
+      <c r="B14" s="9">
+        <f>'Proximal Validation (single)'!B14</f>
+        <v>0.1</v>
+      </c>
+      <c r="C14" s="9">
+        <f>'Proximal Validation (single)'!C14</f>
+        <v>3.665</v>
+      </c>
+      <c r="D14" s="9">
+        <f>'Proximal Validation (single)'!D14</f>
+        <v>1.571</v>
+      </c>
+      <c r="E14" s="9">
+        <f>'Proximal Validation (single)'!E14</f>
+        <v>1.4</v>
+      </c>
+      <c r="F14" s="9">
+        <f>'Proximal Validation (single)'!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <f>'Proximal Validation (single)'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <f>'Proximal Validation (single)'!H14</f>
+        <v>-4.8927497118711504E-4</v>
+      </c>
+      <c r="I14" s="9">
+        <f>'Proximal Validation (single)'!I14</f>
+        <v>3.26927192509174E-2</v>
+      </c>
+      <c r="J14" s="9">
+        <f>'Proximal Validation (single)'!J14</f>
+        <v>-5.8575917035341298E-2</v>
+      </c>
+      <c r="K14" s="9">
+        <f>'Proximal Validation (single)'!K14</f>
+        <v>-1.28835095092654E-2</v>
+      </c>
+      <c r="L14" s="9">
+        <f>'Proximal Validation (single)'!L14</f>
+        <v>-0.29204529523849498</v>
+      </c>
+      <c r="M14" s="9">
+        <f>'Proximal Validation (single)'!M14</f>
+        <v>-0.16083618998527499</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0.33780213456735964</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0.16776454170352398</v>
+      </c>
+      <c r="P14" s="9">
+        <v>3.6132679266206074</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>1.6905697972139977</v>
+      </c>
+      <c r="R14" s="10">
+        <v>1.488496625426333E-4</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" si="2"/>
+        <v>6.2197865432640387E-2</v>
+      </c>
+      <c r="T14" s="8">
+        <f t="shared" si="0"/>
+        <v>6.7764541703523973E-2</v>
+      </c>
+      <c r="U14" s="8">
+        <f t="shared" si="0"/>
+        <v>5.1732073379392673E-2</v>
+      </c>
+      <c r="V14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.11956979721399774</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A15" s="9">
+        <f>'Proximal Validation (single)'!A15</f>
+        <v>0.7</v>
+      </c>
+      <c r="B15" s="9">
+        <f>'Proximal Validation (single)'!B15</f>
+        <v>0.1</v>
+      </c>
+      <c r="C15" s="9">
+        <f>'Proximal Validation (single)'!C15</f>
+        <v>3.665</v>
+      </c>
+      <c r="D15" s="9">
+        <f>'Proximal Validation (single)'!D15</f>
+        <v>1.571</v>
+      </c>
+      <c r="E15" s="9">
+        <f>'Proximal Validation (single)'!E15</f>
+        <v>1.4</v>
+      </c>
+      <c r="F15" s="9">
+        <f>'Proximal Validation (single)'!F15</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <f>'Proximal Validation (single)'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <f>'Proximal Validation (single)'!H15</f>
+        <v>-1.61128584295511E-4</v>
+      </c>
+      <c r="I15" s="9">
+        <f>'Proximal Validation (single)'!I15</f>
+        <v>6.6224433481693296E-2</v>
+      </c>
+      <c r="J15" s="9">
+        <f>'Proximal Validation (single)'!J15</f>
+        <v>-0.118051804602146</v>
+      </c>
+      <c r="K15" s="9">
+        <f>'Proximal Validation (single)'!K15</f>
+        <v>-0.18827667832374601</v>
+      </c>
+      <c r="L15" s="9">
+        <f>'Proximal Validation (single)'!L15</f>
+        <v>-0.57758575677871704</v>
+      </c>
+      <c r="M15" s="9">
+        <f>'Proximal Validation (single)'!M15</f>
+        <v>-0.318100035190582</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0.70709804128240072</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0.13566847021106795</v>
+      </c>
+      <c r="P15" s="9">
+        <v>3.6301089938908273</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>1.5327248396557858</v>
+      </c>
+      <c r="R15" s="10">
+        <v>1.3709255310677041E-4</v>
+      </c>
+      <c r="S15" s="8">
+        <f t="shared" si="2"/>
+        <v>7.0980412824007688E-3</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" si="0"/>
+        <v>3.5668470211067949E-2</v>
+      </c>
+      <c r="U15" s="8">
+        <f t="shared" si="0"/>
+        <v>3.4891006109172729E-2</v>
+      </c>
+      <c r="V15" s="8">
+        <f t="shared" si="0"/>
+        <v>3.8275160344214187E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A16" s="9">
+        <f>'Proximal Validation (single)'!A16</f>
+        <v>0.4</v>
+      </c>
+      <c r="B16" s="9">
+        <f>'Proximal Validation (single)'!B16</f>
+        <v>0.16</v>
+      </c>
+      <c r="C16" s="9">
+        <f>'Proximal Validation (single)'!C16</f>
+        <v>3.665</v>
+      </c>
+      <c r="D16" s="9">
+        <f>'Proximal Validation (single)'!D16</f>
+        <v>1.571</v>
+      </c>
+      <c r="E16" s="9">
+        <f>'Proximal Validation (single)'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <f>'Proximal Validation (single)'!F16</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <f>'Proximal Validation (single)'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <f>'Proximal Validation (single)'!H16</f>
+        <v>3.27638350427151E-4</v>
+      </c>
+      <c r="I16" s="9">
+        <f>'Proximal Validation (single)'!I16</f>
+        <v>4.1303895413875601E-2</v>
+      </c>
+      <c r="J16" s="9">
+        <f>'Proximal Validation (single)'!J16</f>
+        <v>-7.1706265211105305E-2</v>
+      </c>
+      <c r="K16" s="9">
+        <f>'Proximal Validation (single)'!K16</f>
+        <v>-0.16764184832572901</v>
+      </c>
+      <c r="L16" s="9">
+        <f>'Proximal Validation (single)'!L16</f>
+        <v>-0.24127176403999301</v>
+      </c>
+      <c r="M16" s="9">
+        <f>'Proximal Validation (single)'!M16</f>
+        <v>-0.13795974850654599</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0.38509608182577537</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P16" s="9">
+        <v>3.6243567954335902</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>1.7040651600471246</v>
+      </c>
+      <c r="R16" s="10">
+        <v>1.701900036298368E-4</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" si="2"/>
+        <v>1.4903918174224651E-2</v>
+      </c>
+      <c r="T16" s="8">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="U16" s="8">
+        <f t="shared" si="0"/>
+        <v>4.0643204566409796E-2</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" si="0"/>
+        <v>0.13306516004712465</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A17" s="9">
+        <f>'Proximal Validation (single)'!A17</f>
+        <v>0.3</v>
+      </c>
+      <c r="B17" s="9">
+        <f>'Proximal Validation (single)'!B17</f>
+        <v>0.18</v>
+      </c>
+      <c r="C17" s="9">
+        <f>'Proximal Validation (single)'!C17</f>
+        <v>3.665</v>
+      </c>
+      <c r="D17" s="9">
+        <f>'Proximal Validation (single)'!D17</f>
+        <v>1.571</v>
+      </c>
+      <c r="E17" s="9">
+        <f>'Proximal Validation (single)'!E17</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <f>'Proximal Validation (single)'!F17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <f>'Proximal Validation (single)'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <f>'Proximal Validation (single)'!H17</f>
+        <v>3.5051628947258001E-4</v>
+      </c>
+      <c r="I17" s="9">
+        <f>'Proximal Validation (single)'!I17</f>
+        <v>3.2155215740203899E-2</v>
+      </c>
+      <c r="J17" s="9">
+        <f>'Proximal Validation (single)'!J17</f>
+        <v>-5.4656162858009297E-2</v>
+      </c>
+      <c r="K17" s="9">
+        <f>'Proximal Validation (single)'!K17</f>
+        <v>-0.106987468898296</v>
+      </c>
+      <c r="L17" s="9">
+        <f>'Proximal Validation (single)'!L17</f>
+        <v>-0.16471621394157401</v>
+      </c>
+      <c r="M17" s="9">
+        <f>'Proximal Validation (single)'!M17</f>
+        <v>-9.7047880291938796E-2</v>
+      </c>
+      <c r="N17" s="9">
+        <v>0.2858319572850358</v>
+      </c>
+      <c r="O17" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="P17" s="9">
+        <v>3.6206310945485791</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>2.0129848528049687</v>
+      </c>
+      <c r="R17" s="10">
+        <v>4.8249399655614768E-4</v>
+      </c>
+      <c r="S17" s="8">
+        <f t="shared" si="2"/>
+        <v>1.4168042714964191E-2</v>
+      </c>
+      <c r="T17" s="8">
+        <f t="shared" si="0"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="U17" s="8">
+        <f t="shared" si="0"/>
+        <v>4.4368905451420915E-2</v>
+      </c>
+      <c r="V17" s="8">
+        <f t="shared" si="0"/>
+        <v>0.4419848528049688</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="W1:Y1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB5F744-A857-4A50-B613-5F1D0A4C6D83}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1">
+        <v>8.3457410801202102E-4</v>
+      </c>
+      <c r="B1">
+        <v>-3.4524299204349497E-2</v>
+      </c>
+      <c r="C1">
+        <v>-1.46811630111188E-3</v>
+      </c>
+      <c r="D1">
+        <v>0.179403036832809</v>
+      </c>
+      <c r="E1">
+        <v>-7.5630694627761797E-3</v>
+      </c>
+      <c r="F1">
+        <v>0.203822165727615</v>
+      </c>
+      <c r="G1">
+        <v>1.4</v>
+      </c>
+      <c r="H1">
+        <v>0</v>
+      </c>
+      <c r="I1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>-8.0810196232050701E-4</v>
+      </c>
+      <c r="B2">
+        <v>-6.6743046045303303E-2</v>
+      </c>
+      <c r="C2">
+        <v>4.4342974433675398E-4</v>
+      </c>
+      <c r="D2">
+        <v>0.21195751428604101</v>
+      </c>
+      <c r="E2">
+        <v>1.1818818747997299E-3</v>
+      </c>
+      <c r="F2">
+        <v>0.30656093358993503</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>7.8557301312684995E-3</v>
+      </c>
+      <c r="B3">
+        <v>-0.127810284495354</v>
+      </c>
+      <c r="C3">
+        <v>-1.16112818941474E-2</v>
+      </c>
+      <c r="D3">
+        <v>2.8561159968376201E-2</v>
+      </c>
+      <c r="E3">
+        <v>-4.7612398862838697E-2</v>
+      </c>
+      <c r="F3">
+        <v>0.55316102504730202</v>
+      </c>
+      <c r="G3">
+        <v>1.4</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1.1252735275775201E-3</v>
+      </c>
+      <c r="B4">
+        <v>-5.59809319674969E-2</v>
+      </c>
+      <c r="C4">
+        <v>-7.4938102625310399E-4</v>
+      </c>
+      <c r="D4">
+        <v>-3.5423979163169902E-2</v>
+      </c>
+      <c r="E4">
+        <v>-1.04948431253433E-2</v>
+      </c>
+      <c r="F4">
+        <v>0.35301661491393999</v>
+      </c>
+      <c r="G4">
+        <v>1.4</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>-5.5839424021542105E-4</v>
+      </c>
+      <c r="B5">
+        <v>-0.11975701153278399</v>
+      </c>
+      <c r="C5">
+        <v>-9.9074037279933691E-4</v>
+      </c>
+      <c r="D5">
+        <v>-0.19020733237266499</v>
+      </c>
+      <c r="E5">
+        <v>-2.60122120380402E-3</v>
+      </c>
+      <c r="F5">
+        <v>0.66739636659622203</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1.04370433837175E-2</v>
+      </c>
+      <c r="B6">
+        <v>-0.129757210612297</v>
+      </c>
+      <c r="C6">
+        <v>-7.3771281167864799E-3</v>
+      </c>
+      <c r="D6">
+        <v>-0.55726921558380105</v>
+      </c>
+      <c r="E6">
+        <v>-6.0898363590240499E-2</v>
+      </c>
+      <c r="F6">
+        <v>0.32599642872810403</v>
+      </c>
+      <c r="G6">
+        <v>1.4</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>-5.38935419172049E-4</v>
+      </c>
+      <c r="B7">
+        <v>-0.118809439241886</v>
+      </c>
+      <c r="C7">
+        <v>3.4749228507280402E-3</v>
+      </c>
+      <c r="D7">
+        <v>-0.621493339538574</v>
+      </c>
+      <c r="E7">
+        <v>1.56053192913532E-2</v>
+      </c>
+      <c r="F7">
+        <v>0.10576334595680199</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>-7.8150304034352303E-4</v>
+      </c>
+      <c r="B8">
+        <v>4.4897478073835401E-2</v>
+      </c>
+      <c r="C8">
+        <v>-8.2051888108253507E-2</v>
+      </c>
+      <c r="D8">
+        <v>0.48326423764228799</v>
+      </c>
+      <c r="E8">
+        <v>-0.55701375007629395</v>
+      </c>
+      <c r="F8">
+        <v>-0.30146327614784202</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>-4.8895599320530902E-4</v>
+      </c>
+      <c r="B9">
+        <v>4.6247739344835302E-2</v>
+      </c>
+      <c r="C9">
+        <v>-8.3231396973133101E-2</v>
+      </c>
+      <c r="D9">
+        <v>0.33926415443420399</v>
+      </c>
+      <c r="E9">
+        <v>-0.45690825581550598</v>
+      </c>
+      <c r="F9">
+        <v>-0.25065129995346103</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1.7005717381834999E-3</v>
+      </c>
+      <c r="B10">
+        <v>8.4788650274276706E-2</v>
+      </c>
+      <c r="C10">
+        <v>-0.143600359559059</v>
+      </c>
+      <c r="D10">
+        <v>0.28701612353324901</v>
+      </c>
+      <c r="E10">
+        <v>-0.64443814754486095</v>
+      </c>
+      <c r="F10">
+        <v>-0.37070235610008201</v>
+      </c>
+      <c r="G10">
+        <v>1.4</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1.0739560239017001E-3</v>
+      </c>
+      <c r="B11">
+        <v>4.1172292083501802E-2</v>
+      </c>
+      <c r="C11">
+        <v>-6.7707680165767697E-2</v>
+      </c>
+      <c r="D11">
+        <v>0.187965422868729</v>
+      </c>
+      <c r="E11">
+        <v>-0.244067072868347</v>
+      </c>
+      <c r="F11">
+        <v>-0.14198835194110901</v>
+      </c>
+      <c r="G11">
+        <v>1.4</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>-4.8927497118711504E-4</v>
+      </c>
+      <c r="B12">
+        <v>3.26927192509174E-2</v>
+      </c>
+      <c r="C12">
+        <v>-5.8575917035341298E-2</v>
+      </c>
+      <c r="D12">
+        <v>-1.28835095092654E-2</v>
+      </c>
+      <c r="E12">
+        <v>-0.29204529523849498</v>
+      </c>
+      <c r="F12">
+        <v>-0.16083618998527499</v>
+      </c>
+      <c r="G12">
+        <v>1.4</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>-1.61128584295511E-4</v>
+      </c>
+      <c r="B13">
+        <v>6.6224433481693296E-2</v>
+      </c>
+      <c r="C13">
+        <v>-0.118051804602146</v>
+      </c>
+      <c r="D13">
+        <v>-0.18827667832374601</v>
+      </c>
+      <c r="E13">
+        <v>-0.57758575677871704</v>
+      </c>
+      <c r="F13">
+        <v>-0.318100035190582</v>
+      </c>
+      <c r="G13">
+        <v>1.4</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>3.27638350427151E-4</v>
+      </c>
+      <c r="B14">
+        <v>4.1303895413875601E-2</v>
+      </c>
+      <c r="C14">
+        <v>-7.1706265211105305E-2</v>
+      </c>
+      <c r="D14">
+        <v>-0.16764184832572901</v>
+      </c>
+      <c r="E14">
+        <v>-0.24127176403999301</v>
+      </c>
+      <c r="F14">
+        <v>-0.13795974850654599</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>3.5051628947258001E-4</v>
+      </c>
+      <c r="B15">
+        <v>3.2155215740203899E-2</v>
+      </c>
+      <c r="C15">
+        <v>-5.4656162858009297E-2</v>
+      </c>
+      <c r="D15">
+        <v>-0.106987468898296</v>
+      </c>
+      <c r="E15">
+        <v>-0.16471621394157401</v>
+      </c>
+      <c r="F15">
+        <v>-9.7047880291938796E-2</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
-      <c r="H1" s="25" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="28"/>
+      <c r="H1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="27"/>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="28"/>
+    </row>
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -4979,7 +7026,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.203822165727615</v>
       </c>
@@ -5023,7 +7070,7 @@
         <v>0.203822165727615</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0.30656093358993503</v>
       </c>
@@ -5067,7 +7114,7 @@
         <v>0.30656093358993503</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.55316102504730202</v>
       </c>
@@ -5111,7 +7158,7 @@
         <v>0.55316102504730202</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.35301661491393999</v>
       </c>
@@ -5155,7 +7202,7 @@
         <v>0.35301661491393999</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.66739636659622203</v>
       </c>
@@ -5199,7 +7246,7 @@
         <v>0.66739636659622203</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.32599642872810403</v>
       </c>
@@ -5243,7 +7290,7 @@
         <v>0.32599642872810403</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>-0.30146327614784202</v>
       </c>
@@ -5287,7 +7334,7 @@
         <v>-0.30146327614784202</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-0.25065129995346103</v>
       </c>
@@ -5331,7 +7378,7 @@
         <v>-0.25065129995346103</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-0.37070235610008201</v>
       </c>
@@ -5375,7 +7422,7 @@
         <v>-0.37070235610008201</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-0.14198835194110901</v>
       </c>
@@ -5419,7 +7466,7 @@
         <v>-0.14198835194110901</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-0.16083618998527499</v>
       </c>
@@ -5463,7 +7510,7 @@
         <v>-0.16083618998527499</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-0.318100035190582</v>
       </c>
@@ -5507,7 +7554,7 @@
         <v>-0.318100035190582</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-0.13795974850654599</v>
       </c>
@@ -5551,7 +7598,7 @@
         <v>-0.13795974850654599</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>-9.7047880291938796E-2</v>
       </c>
@@ -5595,7 +7642,7 @@
         <v>-9.7047880291938796E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>0.10576334595680199</v>
       </c>
@@ -5639,7 +7686,7 @@
         <v>0.10576334595680199</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H18">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5665,7 +7712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5691,7 +7738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H20">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5717,7 +7764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5743,7 +7790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H22">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5769,7 +7816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5795,7 +7842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5821,7 +7868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5847,7 +7894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H26">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5873,7 +7920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H27">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5899,7 +7946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H28">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5935,14 +7982,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E12580AD17ADB64691A1BA4C2E042DA4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6532fc6a52f3455fe895a4f720bca71c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xmlns:ns4="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9a2f75daf18a7097de825f86ff3fec6" ns3:_="" ns4:_="">
     <xsd:import namespace="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -6195,6 +8234,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6205,23 +8252,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6240,6 +8270,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
